--- a/sampleprojects/CorporateTax/excel/states/MN_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/MN_corp.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t>DT: Determine MN Filing Requirement</t>
   </si>
@@ -70,7 +70,7 @@
     <t>Meets economic nexus threshold ($100K gross receipts); result.mn_gross_receipts is greater than or equal to result.mn_economic_nexus_threshold</t>
   </si>
   <si>
-    <t>result.mn_gross_receipts &gt;= result.mn_economic_nexus_threshold</t>
+    <t>mn_result.gross_receipts &gt;= mn_result.economic_nexus_threshold</t>
   </si>
   <si>
     <t>-</t>
@@ -85,7 +85,7 @@
     <t>Physical nexus - filing required</t>
   </si>
   <si>
-    <t>set result.mn_has_nexus = true;</t>
+    <t>set mn_result.has_nexus = true;</t>
   </si>
   <si>
     <t>X</t>
@@ -97,7 +97,7 @@
     <t>No nexus - no filing required</t>
   </si>
   <si>
-    <t>set result.mn_has_nexus = false; set result.mn_tax_liability = 0.0;</t>
+    <t>set mn_result.has_nexus = false; set mn_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate MN Income Adjustments</t>
@@ -115,19 +115,19 @@
     <t>Has Minnesota nexus</t>
   </si>
   <si>
-    <t>result.mn_has_nexus is equal to true</t>
+    <t>mn_result.has_nexus is equal to true</t>
   </si>
   <si>
     <t>Calculate Minnesota state additions and subtractions; Calculate state-specific income adjustments</t>
   </si>
   <si>
-    <t>set result.mn_state_additions = 0.0; if result.mn_us_interest_income != 0.0 then set result.mn_state_additions = result.mn_state_additions + result.mn_us_interest_income; endif set result.mn_state_subtractions = 0.0; if result.mn_municipal_interest != 0.0 then set result.mn_state_subtractions = result.mn_state_subtractions + result.mn_municipal_interest; endif add (("Minnesota additions: $" + string value of (result.mn_state_additions)) + ", subtractions: $") + string value of (result.mn_state_subtractions) to job.audit_trail;</t>
+    <t>set mn_result.state_additions = 0.0; if mn_result.us_interest_income != 0.0 then set mn_result.state_additions = mn_result.state_additions + mn_result.us_interest_income; endif set mn_result.state_subtractions = 0.0; if mn_result.municipal_interest != 0.0 then set mn_result.state_subtractions = mn_result.state_subtractions + mn_result.municipal_interest; endif add (("Minnesota additions: $" + string value of (mn_result.state_additions)) + ", subtractions: $") + string value of (mn_result.state_subtractions) to job.audit_trail;</t>
   </si>
   <si>
     <t>No nexus - no adjustments</t>
   </si>
   <si>
-    <t>set result.mn_state_additions = 0.0; set result.mn_state_subtractions = 0.0;</t>
+    <t>set mn_result.state_additions = 0.0; set mn_result.state_subtractions = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate MN State Tax</t>
@@ -145,19 +145,19 @@
     <t>Has positive taxable income; result.mn_apportioned_income is greater than 0</t>
   </si>
   <si>
-    <t>result.mn_apportioned_income &gt; 0.0</t>
+    <t>mn_result.apportioned_income &gt; 0.0</t>
   </si>
   <si>
     <t>Calculate Minnesota corporate tax (flat rate 9.5%); Apply Minnesota 9.5% flat rate</t>
   </si>
   <si>
-    <t>set result.mn_taxable_income = the maximum of (result.mn_apportioned_income + result.mn_state_additions - result.mn_state_subtractions) and (0.0); set result.mn_tax_liability = the maximum of (result.mn_taxable_income * result.mn_corp_tax_rate - result.mn_state_credits) and (0.0); set result.mn_refund_or_owed = result.mn_estimated_payments - result.mn_tax_liability; add "Minnesota taxable income: $" + string value of (result.mn_taxable_income) to job.audit_trail; add "Minnesota tax liability (9.5%): $" + string value of (result.mn_tax_liability) to job.audit_trail;</t>
+    <t>set mn_result.taxable_income = the maximum of (mn_result.apportioned_income + mn_result.state_additions - mn_result.state_subtractions) and (0.0); set mn_result.tax_liability = the maximum of (mn_result.taxable_income * mn_result.corp_tax_rate - mn_result.state_credits) and (0.0); set mn_result.refund_or_owed = mn_result.estimated_payments - mn_result.tax_liability; add "Minnesota taxable income: $" + string value of (mn_result.taxable_income) to job.audit_trail; add "Minnesota tax liability (9.5%): $" + string value of (mn_result.tax_liability) to job.audit_trail;</t>
   </si>
   <si>
     <t>No taxable income - no tax liability</t>
   </si>
   <si>
-    <t>set result.mn_taxable_income = 0.0; set result.mn_tax_liability = 0.0;</t>
+    <t>set mn_result.taxable_income = 0.0; set mn_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>No nexus - no tax liability</t>
@@ -205,10 +205,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(8 attributes)</t>
+    <t>mn_apportionment</t>
+  </si>
+  <si>
+    <t>(4 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -238,118 +238,88 @@
     <t>Economic nexus gross receipts threshold - $100K per MN DOR guidance</t>
   </si>
   <si>
+    <t>state_tax_rate</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>Minnesota flat corporate income tax rate: 9.5% (MN Stat. § 290.06)</t>
+  </si>
+  <si>
+    <t>transaction_threshold</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Economic nexus transaction count threshold - 200 transactions</t>
+  </si>
+  <si>
+    <t>mn_result</t>
+  </si>
+  <si>
+    <t>(14 attributes)</t>
+  </si>
+  <si>
+    <t>apportioned_income</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>Declared from decision-table usage; referenced by MN but never declared (campaign #948 Phase 1)</t>
+  </si>
+  <si>
+    <t>corp_tax_rate</t>
+  </si>
+  <si>
+    <t>0.098</t>
+  </si>
+  <si>
+    <t>Form M4 line 10: regular tax = line 9 multiplied by 0.098</t>
+  </si>
+  <si>
+    <t>estimated_payments</t>
+  </si>
+  <si>
+    <t>gross_receipts</t>
+  </si>
+  <si>
+    <t>has_nexus</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>municipal_interest</t>
+  </si>
+  <si>
+    <t>refund_or_owed</t>
+  </si>
+  <si>
     <t>state_additions</t>
   </si>
   <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>State-specific additions: federal interest, IRC 199A addback, foreign dividend deduction, etc.</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>MN</t>
-  </si>
-  <si>
-    <t>Minnesota two-letter state code</t>
-  </si>
-  <si>
     <t>state_credits</t>
   </si>
   <si>
-    <t>State tax credits: R&amp;D, jobs, Angel investment, renewable energy, etc.</t>
-  </si>
-  <si>
     <t>state_subtractions</t>
   </si>
   <si>
-    <t>State-specific subtractions: municipal interest, state taxes, state NOL, small business deduction, etc.</t>
-  </si>
-  <si>
-    <t>state_tax_rate</t>
-  </si>
-  <si>
-    <t>0.095</t>
-  </si>
-  <si>
-    <t>Minnesota flat corporate income tax rate: 9.5% (MN Stat. § 290.06)</t>
-  </si>
-  <si>
-    <t>transaction_threshold</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>Economic nexus transaction count threshold - 200 transactions</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>(14 attributes)</t>
-  </si>
-  <si>
-    <t>mn_apportioned_income</t>
-  </si>
-  <si>
-    <t>Declared from decision-table usage; referenced by MN but never declared (campaign #948 Phase 1)</t>
-  </si>
-  <si>
-    <t>mn_corp_tax_rate</t>
-  </si>
-  <si>
-    <t>0.098</t>
-  </si>
-  <si>
-    <t>Form M4 line 10: regular tax = line 9 multiplied by 0.098</t>
-  </si>
-  <si>
-    <t>mn_economic_nexus_threshold</t>
-  </si>
-  <si>
-    <t>mn_estimated_payments</t>
-  </si>
-  <si>
-    <t>mn_gross_receipts</t>
-  </si>
-  <si>
-    <t>mn_has_nexus</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>mn_municipal_interest</t>
-  </si>
-  <si>
-    <t>mn_refund_or_owed</t>
-  </si>
-  <si>
-    <t>mn_state_additions</t>
-  </si>
-  <si>
-    <t>mn_state_credits</t>
-  </si>
-  <si>
-    <t>mn_state_subtractions</t>
-  </si>
-  <si>
-    <t>mn_tax_liability</t>
-  </si>
-  <si>
-    <t>mn_taxable_income</t>
-  </si>
-  <si>
-    <t>mn_us_interest_income</t>
+    <t>tax_liability</t>
+  </si>
+  <si>
+    <t>taxable_income</t>
+  </si>
+  <si>
+    <t>us_interest_income</t>
   </si>
 </sst>
 </file>
@@ -2701,14 +2671,14 @@
       <c r="B7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>65</v>
+      <c r="C7" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
@@ -2717,7 +2687,7 @@
         <v>67</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -2736,194 +2706,194 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H8" s="16" t="s">
+      <c r="A8" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>8</v>
-      </c>
+      <c r="B8" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="D9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>67</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="7" t="s">
+      <c r="D10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="I11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="H10" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="H12" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>70</v>
@@ -2932,7 +2902,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>8</v>
@@ -2941,7 +2911,7 @@
         <v>67</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>8</v>
@@ -2964,16 +2934,16 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>70</v>
+        <v>90</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>91</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>8</v>
@@ -2982,7 +2952,7 @@
         <v>67</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I14" s="8" t="s">
         <v>8</v>
@@ -3005,7 +2975,7 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>70</v>
@@ -3014,7 +2984,7 @@
         <v>8</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>8</v>
@@ -3023,7 +2993,7 @@
         <v>67</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>8</v>
@@ -3046,7 +3016,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>70</v>
@@ -3055,7 +3025,7 @@
         <v>8</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>8</v>
@@ -3064,7 +3034,7 @@
         <v>67</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>8</v>
@@ -3087,7 +3057,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>70</v>
@@ -3096,7 +3066,7 @@
         <v>8</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>8</v>
@@ -3105,7 +3075,7 @@
         <v>67</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>8</v>
@@ -3128,16 +3098,16 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>101</v>
+        <v>96</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>8</v>
@@ -3146,7 +3116,7 @@
         <v>67</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I18" s="8" t="s">
         <v>8</v>
@@ -3169,7 +3139,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>70</v>
@@ -3178,7 +3148,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>8</v>
@@ -3187,7 +3157,7 @@
         <v>67</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>8</v>
@@ -3210,7 +3180,7 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>70</v>
@@ -3219,7 +3189,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>8</v>
@@ -3228,7 +3198,7 @@
         <v>67</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I20" s="8" t="s">
         <v>8</v>
@@ -3251,7 +3221,7 @@
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>70</v>
@@ -3260,7 +3230,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>8</v>
@@ -3269,7 +3239,7 @@
         <v>67</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>8</v>
@@ -3292,7 +3262,7 @@
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>70</v>
@@ -3301,7 +3271,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>8</v>
@@ -3310,7 +3280,7 @@
         <v>67</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="I22" s="8" t="s">
         <v>8</v>
@@ -3325,170 +3295,6 @@
         <v>8</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H23" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M26" s="8" t="s">
         <v>8</v>
       </c>
     </row>
